--- a/results/samplewalking/sample/reference_peaks.xlsx
+++ b/results/samplewalking/sample/reference_peaks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C296"/>
+  <dimension ref="A1:C291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8944586920950225</v>
+        <v>0.8280626178550434</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9214998516481792</v>
+        <v>0.5600666850279427</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.035774822491899</v>
+        <v>0.8630238020076396</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.087095741274416</v>
+        <v>0.8781879227740139</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.210785912158092</v>
+        <v>0.9197830261737415</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.130910938964239</v>
+        <v>0.9770926650933925</v>
       </c>
     </row>
     <row r="8">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.130514354875193</v>
+        <v>0.9885462489004345</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.117647404430578</v>
+        <v>0.9859917856987626</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.186990866815312</v>
+        <v>0.9847474825244348</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.215207090335977</v>
+        <v>0.923734351863732</v>
       </c>
     </row>
     <row r="12">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.152091466979233</v>
+        <v>1.034419520738145</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.107439036212534</v>
+        <v>1.052444136309543</v>
       </c>
     </row>
     <row r="14">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.167352610257721</v>
+        <v>0.9796333137446004</v>
       </c>
     </row>
     <row r="15">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.229733818634752</v>
+        <v>0.963693387818359</v>
       </c>
     </row>
     <row r="16">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.160243473254075</v>
+        <v>1.017870192066948</v>
       </c>
     </row>
     <row r="17">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.267556190090098</v>
+        <v>1.061857556723196</v>
       </c>
     </row>
     <row r="18">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.09423425487725</v>
+        <v>0.9932750757654567</v>
       </c>
     </row>
     <row r="19">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.140017684712711</v>
+        <v>0.9252495895289453</v>
       </c>
     </row>
     <row r="20">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.160037837059755</v>
+        <v>0.9686080672793244</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.128399239733613</v>
+        <v>0.9757386823451275</v>
       </c>
     </row>
     <row r="22">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.161477290419997</v>
+        <v>1.021935221537042</v>
       </c>
     </row>
     <row r="23">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.178133822159944</v>
+        <v>0.9822250168756425</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.186608971025865</v>
+        <v>1.049523770608851</v>
       </c>
     </row>
     <row r="25">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.194129380418146</v>
+        <v>1.099292895038755</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.181864650256898</v>
+        <v>1.067352296424389</v>
       </c>
     </row>
     <row r="27">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.158980279488968</v>
+        <v>1.079300460318597</v>
       </c>
     </row>
     <row r="28">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.179059185034385</v>
+        <v>1.136822805410632</v>
       </c>
     </row>
     <row r="29">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.219863281307376</v>
+        <v>1.144715165534703</v>
       </c>
     </row>
     <row r="30">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.16511998871938</v>
+        <v>1.028677805751345</v>
       </c>
     </row>
     <row r="31">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.12762075985512</v>
+        <v>1.107257567705305</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.137109401393038</v>
+        <v>1.010662574344343</v>
       </c>
     </row>
     <row r="33">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.165222806816546</v>
+        <v>1.097247916505599</v>
       </c>
     </row>
     <row r="34">
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1.14912443046118</v>
+        <v>1.153466085875865</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.119556883377835</v>
+        <v>1.158467587523583</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.155616658881865</v>
+        <v>1.067118748243558</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.143454746817781</v>
+        <v>1.204852996100837</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.166809143172731</v>
+        <v>1.139027349968609</v>
       </c>
     </row>
     <row r="39">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.205615630700902</v>
+        <v>1.050510878559744</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.220465501590743</v>
+        <v>1.03540490629504</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.122817685887775</v>
+        <v>1.084592309518858</v>
       </c>
     </row>
     <row r="42">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.112741512366073</v>
+        <v>1.072408246707347</v>
       </c>
     </row>
     <row r="43">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.144541680987759</v>
+        <v>1.037061178647451</v>
       </c>
     </row>
     <row r="44">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.151827077586536</v>
+        <v>1.09867433800227</v>
       </c>
     </row>
     <row r="45">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.234786593695194</v>
+        <v>1.077092256480523</v>
       </c>
     </row>
     <row r="46">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.093955177184958</v>
+        <v>1.015656106201021</v>
       </c>
     </row>
     <row r="47">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.146083952445162</v>
+        <v>1.022365575164337</v>
       </c>
     </row>
     <row r="48">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.1725669566137</v>
+        <v>1.07820730189954</v>
       </c>
     </row>
     <row r="49">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.170407776573337</v>
+        <v>1.120938529749401</v>
       </c>
     </row>
     <row r="50">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.21394389657087</v>
+        <v>1.102150993522109</v>
       </c>
     </row>
     <row r="51">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.203911787947944</v>
+        <v>0.9569716346631115</v>
       </c>
     </row>
     <row r="52">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.136595310907237</v>
+        <v>1.004124127242568</v>
       </c>
     </row>
     <row r="53">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.140854917789588</v>
+        <v>1.067036462378396</v>
       </c>
     </row>
     <row r="54">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.074008466335892</v>
+        <v>0.9580368456276205</v>
       </c>
     </row>
     <row r="55">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.153075583052052</v>
+        <v>1.017086549705222</v>
       </c>
     </row>
     <row r="56">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.149388819853881</v>
+        <v>0.8874642469208434</v>
       </c>
     </row>
     <row r="57">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.139459529328125</v>
+        <v>1.044214201547135</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.205645007300085</v>
+        <v>1.204296063373481</v>
       </c>
     </row>
     <row r="59">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.167235103860966</v>
+        <v>1.141565128835882</v>
       </c>
     </row>
     <row r="60">
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.171054061755487</v>
+        <v>1.033634922901404</v>
       </c>
     </row>
     <row r="61">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.135288052243344</v>
+        <v>1.207109968100338</v>
       </c>
     </row>
     <row r="62">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1.134436130866874</v>
+        <v>1.055667424364861</v>
       </c>
     </row>
     <row r="63">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1.227985910983029</v>
+        <v>1.001351521958826</v>
       </c>
     </row>
     <row r="64">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1.194863795397862</v>
+        <v>1.033213077578047</v>
       </c>
     </row>
     <row r="65">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1.102004365362639</v>
+        <v>1.047997147849199</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.202325451591771</v>
+        <v>1.145025376608353</v>
       </c>
     </row>
     <row r="67">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1.125916917102175</v>
+        <v>1.167964361064964</v>
       </c>
     </row>
     <row r="68">
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1.190883266207804</v>
+        <v>0.9409613928203924</v>
       </c>
     </row>
     <row r="69">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.135493688437664</v>
+        <v>1.06592543981219</v>
       </c>
     </row>
     <row r="70">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.140032373012306</v>
+        <v>1.135054826912372</v>
       </c>
     </row>
     <row r="71">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.220876773979384</v>
+        <v>1.022910990926085</v>
       </c>
     </row>
     <row r="72">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.134568325563224</v>
+        <v>1.052139410917539</v>
       </c>
     </row>
     <row r="73">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1.14471794058289</v>
+        <v>0.9770902635258956</v>
       </c>
     </row>
     <row r="74">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.161697614913906</v>
+        <v>1.071071043561278</v>
       </c>
     </row>
     <row r="75">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1.145232031068691</v>
+        <v>1.020754296856605</v>
       </c>
     </row>
     <row r="76">
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.172052866127903</v>
+        <v>1.032005417747782</v>
       </c>
     </row>
     <row r="77">
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.194643470903947</v>
+        <v>0.9606904940317694</v>
       </c>
     </row>
     <row r="78">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.104486687994078</v>
+        <v>1.13855521631793</v>
       </c>
     </row>
     <row r="79">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1.078194631720264</v>
+        <v>1.050989314561995</v>
       </c>
     </row>
     <row r="80">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.174402994062989</v>
+        <v>1.008486684660042</v>
       </c>
     </row>
     <row r="81">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1.173639202484085</v>
+        <v>1.010391032957783</v>
       </c>
     </row>
     <row r="82">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1.173742020581245</v>
+        <v>0.9930108976540504</v>
       </c>
     </row>
     <row r="83">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.178251328556698</v>
+        <v>0.8894062409975532</v>
       </c>
     </row>
     <row r="84">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1.141398384874573</v>
+        <v>0.99919539129091</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1.137403167384924</v>
+        <v>1.157519367384711</v>
       </c>
     </row>
     <row r="86">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.173595137585302</v>
+        <v>0.9237789734850165</v>
       </c>
     </row>
     <row r="87">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.180483950095033</v>
+        <v>1.068597007936629</v>
       </c>
     </row>
     <row r="88">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1.216279336206369</v>
+        <v>1.1493403432908</v>
       </c>
     </row>
     <row r="89">
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1.165472507909644</v>
+        <v>1.090582852382229</v>
       </c>
     </row>
     <row r="90">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1.250135866771247</v>
+        <v>1.248243539928813</v>
       </c>
     </row>
     <row r="91">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1.192675238758307</v>
+        <v>1.088539847545849</v>
       </c>
     </row>
     <row r="92">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1.219745774910622</v>
+        <v>1.110363129573842</v>
       </c>
     </row>
     <row r="93">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1.164811534427905</v>
+        <v>0.9613630212079742</v>
       </c>
     </row>
     <row r="94">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1.193541848434363</v>
+        <v>1.085809605202768</v>
       </c>
     </row>
     <row r="95">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1.164767469529122</v>
+        <v>1.049278842078389</v>
       </c>
     </row>
     <row r="96">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1.174256111067046</v>
+        <v>1.232187474375098</v>
       </c>
     </row>
     <row r="97">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1.138681049449629</v>
+        <v>1.111086362372449</v>
       </c>
     </row>
     <row r="98">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1.239178395273893</v>
+        <v>1.07981348699806</v>
       </c>
     </row>
     <row r="99">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1.197081728636602</v>
+        <v>1.111084878766287</v>
       </c>
     </row>
     <row r="100">
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1.15323715434759</v>
+        <v>1.038888541668056</v>
       </c>
     </row>
     <row r="101">
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1.146553978032179</v>
+        <v>0.9906575159345334</v>
       </c>
     </row>
     <row r="102">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1.200254401348971</v>
+        <v>0.9938860911745167</v>
       </c>
     </row>
     <row r="103">
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1.152987453254486</v>
+        <v>1.049764681432581</v>
       </c>
     </row>
     <row r="104">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1.145775498153681</v>
+        <v>1.074508584438808</v>
       </c>
     </row>
     <row r="105">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1.206834759567224</v>
+        <v>0.9229339408363445</v>
       </c>
     </row>
     <row r="106">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1.101446209978056</v>
+        <v>1.158614166683987</v>
       </c>
     </row>
     <row r="107">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1.150975156210066</v>
+        <v>1.01683739182766</v>
       </c>
     </row>
     <row r="108">
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1.09028310228637</v>
+        <v>0.9755267150693467</v>
       </c>
     </row>
     <row r="109">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1.131953808235453</v>
+        <v>1.120099865603118</v>
       </c>
     </row>
     <row r="110">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1.196171054061755</v>
+        <v>1.011925036654346</v>
       </c>
     </row>
     <row r="111">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1.139606412324071</v>
+        <v>1.110064496392347</v>
       </c>
     </row>
     <row r="112">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1.122127335806843</v>
+        <v>1.035837111494152</v>
       </c>
     </row>
     <row r="113">
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1.16758762305124</v>
+        <v>0.9711205310057068</v>
       </c>
     </row>
     <row r="114">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1.185096076167646</v>
+        <v>1.093128106286083</v>
       </c>
     </row>
     <row r="115">
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1.162990185278221</v>
+        <v>1.007772504123121</v>
       </c>
     </row>
     <row r="116">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1.090738439573804</v>
+        <v>1.064116636579421</v>
       </c>
     </row>
     <row r="117">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1.154191893821215</v>
+        <v>1.041732984908927</v>
       </c>
     </row>
     <row r="118">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1.190134162928491</v>
+        <v>0.9626897949235518</v>
       </c>
     </row>
     <row r="119">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1.170628101067252</v>
+        <v>0.9686019416566189</v>
       </c>
     </row>
     <row r="120">
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1.135611194834458</v>
+        <v>1.023082736676843</v>
       </c>
     </row>
     <row r="121">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1.136360298113712</v>
+        <v>0.9294012814647249</v>
       </c>
     </row>
     <row r="122">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1.120717259045789</v>
+        <v>0.9485663053307499</v>
       </c>
     </row>
     <row r="123">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1.107585919208477</v>
+        <v>1.004749313265481</v>
       </c>
     </row>
     <row r="124">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1.146142705643538</v>
+        <v>1.068590603752748</v>
       </c>
     </row>
     <row r="125">
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1.140311450704598</v>
+        <v>0.9922503864153132</v>
       </c>
     </row>
     <row r="126">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1.166662260176788</v>
+        <v>0.9943375539543687</v>
       </c>
     </row>
     <row r="127">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1.094146125079684</v>
+        <v>0.9857755967913272</v>
       </c>
     </row>
     <row r="128">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1.153266530946767</v>
+        <v>1.067670252603903</v>
       </c>
     </row>
     <row r="129">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1.119439376981084</v>
+        <v>0.9363203296964386</v>
       </c>
     </row>
     <row r="130">
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1.156365762161174</v>
+        <v>1.125969009755875</v>
       </c>
     </row>
     <row r="131">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1.134818026656326</v>
+        <v>0.9603790082438054</v>
       </c>
     </row>
     <row r="132">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1.164356197140482</v>
+        <v>1.041581747453023</v>
       </c>
     </row>
     <row r="133">
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1.141574644469708</v>
+        <v>1.07310986147995</v>
       </c>
     </row>
     <row r="134">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1.128017343944161</v>
+        <v>1.030649529223898</v>
       </c>
     </row>
     <row r="135">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1.10848190548373</v>
+        <v>1.200140220266272</v>
       </c>
     </row>
     <row r="136">
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1.15429471191838</v>
+        <v>1.054151287803535</v>
       </c>
     </row>
     <row r="137">
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1.23361152972765</v>
+        <v>0.96431499549371</v>
       </c>
     </row>
     <row r="138">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1.145907692850011</v>
+        <v>0.9133570166274726</v>
       </c>
     </row>
     <row r="139">
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1.115972938276831</v>
+        <v>0.9604536689082525</v>
       </c>
     </row>
     <row r="140">
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1.126107864996898</v>
+        <v>1.15165861386254</v>
       </c>
     </row>
     <row r="141">
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1.106058336050674</v>
+        <v>1.038206895420078</v>
       </c>
     </row>
     <row r="142">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1.074228790829801</v>
+        <v>0.9382063346427945</v>
       </c>
     </row>
     <row r="143">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1.11260931766973</v>
+        <v>0.8447262891671294</v>
       </c>
     </row>
     <row r="144">
@@ -2301,64 +2301,64 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1.092706671719442</v>
+        <v>0.8472920538986926</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0.9988043724130231</v>
+        <v>0.4417137548467759</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0.9874650051262164</v>
+        <v>0.8832077824895628</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>145</v>
+        <v>2</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1.005281912534187</v>
+        <v>0.7862148031334978</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>0.551060935879697</v>
+        <v>0.8956535586985718</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -2366,12 +2366,12 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0.4763268675438519</v>
+        <v>0.9721436261692561</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -2379,12 +2379,12 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0.8179032746095115</v>
+        <v>1.079216248182339</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -2392,12 +2392,12 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0.949627945371276</v>
+        <v>0.9852834999618505</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -2405,12 +2405,12 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0.9763312740337302</v>
+        <v>0.9900970581385797</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -2418,12 +2418,12 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1.080779772448863</v>
+        <v>0.9403453071372148</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -2431,12 +2431,12 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1.160228784954481</v>
+        <v>1.16304663951348</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -2444,12 +2444,12 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1.117368326738287</v>
+        <v>0.9816036946258194</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -2457,12 +2457,12 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1.137579426980056</v>
+        <v>1.047828829641946</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -2470,12 +2470,12 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1.13929795803259</v>
+        <v>1.062487309166346</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -2483,12 +2483,12 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1.139327334631779</v>
+        <v>1.073036103309028</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1.107350906414968</v>
+        <v>1.064166886338175</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -2509,12 +2509,12 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1.124080879652886</v>
+        <v>0.9866796172681291</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -2522,12 +2522,12 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1.105558933864462</v>
+        <v>1.015575910863711</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -2535,12 +2535,12 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1.111008293013951</v>
+        <v>1.05973720318259</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -2548,12 +2548,12 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1.12910427811414</v>
+        <v>1.119174106305846</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -2561,12 +2561,12 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1.11963032487581</v>
+        <v>1.171992403430885</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -2574,12 +2574,12 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1.120496934551874</v>
+        <v>1.008160814352739</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -2587,12 +2587,12 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1.117133313944778</v>
+        <v>1.019793930740797</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -2600,12 +2600,12 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1.116751418155326</v>
+        <v>0.9940874335453163</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -2613,12 +2613,12 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1.094498644269947</v>
+        <v>0.9717456159279948</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -2626,12 +2626,12 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1.082057654513569</v>
+        <v>0.9845433316073682</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -2639,12 +2639,12 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1.080221617064279</v>
+        <v>0.9919474945690017</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -2652,12 +2652,12 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1.09092938746853</v>
+        <v>1.031304874423967</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -2665,12 +2665,12 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1.08296832908842</v>
+        <v>1.000548868225931</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -2678,12 +2678,12 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1.06568020046591</v>
+        <v>1.021307316520852</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -2691,12 +2691,12 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1.08182264172006</v>
+        <v>1.165505672721112</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -2704,12 +2704,12 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1.106102400949452</v>
+        <v>1.149565281847249</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -2717,12 +2717,12 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1.094410514472379</v>
+        <v>1.118988438610053</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -2730,12 +2730,12 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1.118205559815162</v>
+        <v>1.040210280173245</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -2743,12 +2743,12 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1.09511555285291</v>
+        <v>1.115785942163616</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -2756,12 +2756,12 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1.119880025968913</v>
+        <v>1.044327435110417</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -2769,12 +2769,12 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1.058306674069569</v>
+        <v>1.080754796448439</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -2782,12 +2782,12 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1.055045871559629</v>
+        <v>1.012928498617526</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1.08574441771174</v>
+        <v>1.143515307060437</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -2808,12 +2808,12 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1.156439203659149</v>
+        <v>1.157671831188496</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -2821,12 +2821,12 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1.096437499816403</v>
+        <v>1.114381648277607</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -2834,12 +2834,12 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1.123434594470742</v>
+        <v>1.275610806117301</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -2847,12 +2847,12 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1.117676781029769</v>
+        <v>1.184010701865413</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -2860,12 +2860,12 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1.1563070089628</v>
+        <v>1.105685042429106</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -2873,12 +2873,12 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1.18204090985203</v>
+        <v>1.112187962231647</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -2886,12 +2886,12 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1.195054743292588</v>
+        <v>1.075704076406981</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -2899,12 +2899,12 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1.115781990382096</v>
+        <v>1.044327154793343</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -2912,12 +2912,12 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1.122612049693455</v>
+        <v>1.116296828723699</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -2925,12 +2925,12 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1.108437840584947</v>
+        <v>1.06036246443868</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -2938,12 +2938,12 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1.188019047786914</v>
+        <v>1.079346170510449</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -2951,12 +2951,12 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1.122788309288581</v>
+        <v>1.062056352379201</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -2964,12 +2964,12 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1.130014952688987</v>
+        <v>1.283985950768523</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -2977,12 +2977,12 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1.128693005725498</v>
+        <v>1.173869579518789</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -2990,12 +2990,12 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1.105882076455537</v>
+        <v>1.137111793350441</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -3003,12 +3003,12 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1.123904620057751</v>
+        <v>1.189234233038136</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -3016,12 +3016,12 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1.138607607951658</v>
+        <v>1.061154693628905</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -3029,12 +3029,12 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1.133966105279854</v>
+        <v>1.152893117269728</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -3042,12 +3042,12 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1.104398558196512</v>
+        <v>1.039874712329108</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -3055,12 +3055,12 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1.020895575002864</v>
+        <v>1.03042110301643</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -3068,12 +3068,12 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1.084128704756365</v>
+        <v>1.152169479626821</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -3081,12 +3081,12 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1.097906329775827</v>
+        <v>1.071433151509757</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -3094,12 +3094,12 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1.094792410261834</v>
+        <v>1.007732614663472</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -3107,12 +3107,12 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1.161154147828922</v>
+        <v>1.060198729240992</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -3120,12 +3120,12 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1.148301885683902</v>
+        <v>1.038322689124177</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -3133,12 +3133,12 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1.086728533784558</v>
+        <v>1.04986315280864</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -3146,12 +3146,12 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1.114401290220236</v>
+        <v>0.9458258171332842</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -3159,12 +3159,12 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1.129677121798318</v>
+        <v>1.047974683647343</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -3172,12 +3172,12 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1.121701375118608</v>
+        <v>1.158399700175806</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -3185,12 +3185,12 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1.11611982127277</v>
+        <v>1.026590951470748</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -3198,12 +3198,12 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1.028841945083385</v>
+        <v>1.044207549738356</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -3211,12 +3211,12 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1.148463456979439</v>
+        <v>1.077953261557311</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -3224,12 +3224,12 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1.125035619126516</v>
+        <v>1.260532466285622</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -3237,12 +3237,12 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1.12112853143443</v>
+        <v>1.130275583351013</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -3250,12 +3250,12 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1.045557230021709</v>
+        <v>1.186389123527877</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -3263,12 +3263,12 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1.121055089936458</v>
+        <v>1.119747799343974</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -3276,12 +3276,12 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1.116766106454917</v>
+        <v>0.9486310945477013</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -3289,12 +3289,12 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1.079310942489432</v>
+        <v>1.074695755850218</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -3302,12 +3302,12 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1.090488738480701</v>
+        <v>1.140215014380736</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -3315,12 +3315,12 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>1.082659874796934</v>
+        <v>0.9598222906340607</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -3328,12 +3328,12 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1.073700012044406</v>
+        <v>1.065577424949907</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -3341,12 +3341,12 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>1.127136045968502</v>
+        <v>1.037892819406768</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -3354,12 +3354,12 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>1.114783186009688</v>
+        <v>0.887339068658404</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -3367,12 +3367,12 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>1.115179770098735</v>
+        <v>1.044188795225116</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -3380,12 +3380,12 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>1.104178233702597</v>
+        <v>1.025182418551418</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -3393,12 +3393,12 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>1.070894546821892</v>
+        <v>0.9098513041243529</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -3406,12 +3406,12 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1.125960982000958</v>
+        <v>1.007479090579332</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -3419,12 +3419,12 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>1.151136727505603</v>
+        <v>1.16657199536919</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -3432,12 +3432,12 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1.141089930583096</v>
+        <v>0.9883414747301287</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -3445,12 +3445,12 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1.074831011113167</v>
+        <v>0.9229987208727745</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -3458,12 +3458,12 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1.094792410261834</v>
+        <v>0.9666294596867752</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -3471,12 +3471,12 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1.136683440704803</v>
+        <v>0.9752497963578104</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -3484,12 +3484,12 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1.10742434791294</v>
+        <v>0.9988429416258322</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -3497,12 +3497,12 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1.124448087142744</v>
+        <v>1.186847037160205</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -3510,12 +3510,12 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1.157966786816957</v>
+        <v>1.186847037160205</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -3523,12 +3523,12 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1.24825576442318</v>
+        <v>1.186847037160205</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -3536,12 +3536,12 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1.180939287382457</v>
+        <v>1.186847037160205</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -3549,12 +3549,12 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1.136492492810077</v>
+        <v>1.046285867893876</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -3562,12 +3562,12 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1.126431007587975</v>
+        <v>0.9780965778533848</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -3575,12 +3575,12 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1.173125111998284</v>
+        <v>1.069198929552033</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -3588,12 +3588,12 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>1.16769044114839</v>
+        <v>0.9131817749836407</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>1.095541513541143</v>
+        <v>1.092594797818462</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -3614,12 +3614,12 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>1.140340827303786</v>
+        <v>1.029422459944031</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -3627,12 +3627,12 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1.107850308601165</v>
+        <v>1.064529550113388</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -3640,12 +3640,12 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>1.061464658482346</v>
+        <v>1.222685607373795</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -3653,12 +3653,12 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>1.121084466535647</v>
+        <v>1.116759990250977</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -3666,12 +3666,12 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>1.12804672054335</v>
+        <v>0.9897203379414372</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -3679,12 +3679,12 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>1.1219804528109</v>
+        <v>1.071816474548247</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -3692,12 +3692,12 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>1.118984039693661</v>
+        <v>1.052270308087512</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -3705,12 +3705,12 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>1.096555006213151</v>
+        <v>1.229941721018894</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>1.117618027831395</v>
+        <v>1.042118736857648</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -3731,12 +3731,12 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>1.102459702650063</v>
+        <v>1.210329983152509</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -3744,12 +3744,12 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>1.104163545402983</v>
+        <v>1.077797740838336</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -3757,12 +3757,12 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>1.088314870140743</v>
+        <v>1.02873983286182</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -3770,12 +3770,12 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>1.071702403299579</v>
+        <v>1.014442040673434</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -3783,12 +3783,12 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>1.12685696827621</v>
+        <v>0.9668018632364647</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -3796,12 +3796,12 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>1.112065850584741</v>
+        <v>1.01989577699227</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -3809,12 +3809,12 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1.099742367225097</v>
+        <v>1.080708519617682</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -3822,12 +3822,12 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1.114254407224293</v>
+        <v>1.17624287319152</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -3835,12 +3835,12 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>1.136110597020625</v>
+        <v>1.028438774148382</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -3848,12 +3848,12 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>1.035113849010178</v>
+        <v>1.062575790745185</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -3861,12 +3861,12 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>1.092971061112139</v>
+        <v>0.7726756191914335</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -3874,12 +3874,12 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>1.07389095993915</v>
+        <v>1.096790728358314</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -3887,12 +3887,12 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>1.111478318600969</v>
+        <v>1.141745703649313</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -3900,12 +3900,12 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>1.140223320907032</v>
+        <v>1.108809102268566</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -3913,12 +3913,12 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>1.164973105723443</v>
+        <v>1.182955784656914</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -3926,12 +3926,12 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>1.105749881759188</v>
+        <v>1.181789490453937</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -3939,12 +3939,12 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>1.099052017144183</v>
+        <v>1.056599117664275</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -3952,12 +3952,12 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>1.062536904352731</v>
+        <v>1.115152638389632</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -3965,12 +3965,12 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>1.157643644225854</v>
+        <v>1.024175584295178</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -3978,12 +3978,12 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>1.138049452567061</v>
+        <v>1.170163507101288</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -3991,12 +3991,12 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>1.041943908321509</v>
+        <v>0.9914963870398297</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -4004,12 +4004,12 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>1.051814445648885</v>
+        <v>1.279043110403768</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>1.067501549615607</v>
+        <v>1.125644013650915</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -4030,12 +4030,12 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>1.115502912689796</v>
+        <v>1.092771216465297</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -4043,12 +4043,12 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>1.114636303013745</v>
+        <v>1.069043166100758</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -4056,12 +4056,12 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>1.115649795685748</v>
+        <v>0.9952041881544527</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -4069,12 +4069,12 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>1.110846721718413</v>
+        <v>1.010532553041569</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -4082,12 +4082,12 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>1.075359789898554</v>
+        <v>0.9082927860430493</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -4095,12 +4095,12 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>1.059320166741577</v>
+        <v>1.192031246216604</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -4108,12 +4108,12 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>1.129163031312525</v>
+        <v>1.008171244730919</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -4121,12 +4121,12 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>1.153780621432579</v>
+        <v>0.9152198704682475</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -4134,12 +4134,12 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>1.087154494472786</v>
+        <v>1.22052004154778</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -4147,12 +4147,12 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>1.069690106255192</v>
+        <v>1.069080997628163</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -4160,12 +4160,12 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>1.094028618682928</v>
+        <v>1.287367860435789</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -4173,12 +4173,12 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>1.125285320219624</v>
+        <v>1.03987199894994</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -4186,12 +4186,12 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>1.111669266495709</v>
+        <v>0.8574656754930834</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -4199,12 +4199,12 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>1.132188821028978</v>
+        <v>0.9843635389625708</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -4212,72 +4212,7 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>1.094851163460211</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="n">
-        <v>143</v>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C292" t="n">
-        <v>1.093015126010922</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="n">
-        <v>144</v>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C293" t="n">
-        <v>0.9275661193806346</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="n">
-        <v>145</v>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C294" t="n">
-        <v>0.9201632163851107</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>146</v>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C295" t="n">
-        <v>0.7622493074467079</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>147</v>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C296" t="n">
-        <v>0.5085383085541719</v>
+        <v>0.7793977392828925</v>
       </c>
     </row>
   </sheetData>
